--- a/outputs/440-24.xlsx
+++ b/outputs/440-24.xlsx
@@ -178,15 +178,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
